--- a/5月22日峰会/导出文件/2026峰会会务名单.xlsx
+++ b/5月22日峰会/导出文件/2026峰会会务名单.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026 人工智能商业化落地与硬核投资破局峰会</t>
+          <t>2026 人工智能商业化落地与硬核投资破局峰会（官方最终定稿议程）</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>北大经院上海校友会、复旦大学住房政策研究中心</t>
+          <t>北京大学经济学院上海校友会、复旦大学住房政策研究中心</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>复旦大学未来信息创新学院、上海市云计算创新基地、杨浦区科企联、虹口区科企联、中国商业文化研究会长三角分会、东投资联盟、红瓦（陆家嘴）共创中心</t>
+          <t>复旦大学未来信息创新学院、上海市云计算创新基地、上海市杨浦区科技企业联合会、上海市虹口区科技企业联合会、中国商业文化研究会长三角分会、东投资联盟、红瓦（陆家嘴）共创中心</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>腾讯云、福布斯中国人工智能科技企业评选委</t>
+          <t>腾讯云、福布斯中国人工智能科技企业评选委员会</t>
         </is>
       </c>
     </row>
@@ -608,82 +608,94 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>特约赞助商</t>
+          <t>晚宴名称</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>蔚来、泰隆银行</t>
+          <t>【绿城·潮鸣】星耀北外滩——AI 领袖定制晚宴（凭专属邀请码入场）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>赞助方</t>
+          <t>特约赞助商</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>茶活力、美年大健康、复金汇、古井贡酒·年份原浆</t>
+          <t>蔚来汽车、泰隆银行</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>媒体支持</t>
+          <t>赞助方</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>新华网、人民网、央视网、央广网、中新网、上海证券报、上海电视台、财联社、上海虹口、上海杨浦、左明右理</t>
+          <t>茶活力、美年大健康、复金汇、古井贡酒·年份原浆</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>总联系人</t>
+          <t>媒体支持</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>胡继刚 13262607888</t>
+          <t>新华网、人民网、央视网、央广网、中新网、上海证券报、上海电视台、财联社、上海虹口、上海杨浦、左明右理</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>VIP 接待</t>
+          <t>总联系人</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>王珏 13817642219</t>
+          <t>胡继刚 13262607888</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>现场总协调</t>
+          <t>VIP 接待</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>黄欣（北大经院上海校友会秘书长）</t>
+          <t>王珏 13817642219</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>现场总协调</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>黄欣（北京大学经济学院上海校友会秘书长）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>整体校对</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>安淑娟 13661612711</t>
         </is>
@@ -770,7 +782,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>晚宴冠名 / 5 席 VIP / 礼品 / 背景板</t>
+          <t>晚宴冠名【绿城·潮鸣】/ 邀请码核验 / 礼品 / 背景板</t>
         </is>
       </c>
     </row>
@@ -797,7 +809,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>战略合作 / 主舞台 LOGO / 易拉宝 / 礼品</t>
+          <t>华东区渠道总经理 / 战略合作 / 圆桌二嘉宾</t>
         </is>
       </c>
     </row>
@@ -809,7 +821,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>福布斯中国 AI 评选委</t>
+          <t>福布斯中国人工智能科技企业评选委员会</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -824,7 +836,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>颁奖典礼物料</t>
+          <t>★ 颁奖典礼物料（14:25-14:40 启用）</t>
         </is>
       </c>
     </row>
@@ -836,7 +848,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>蔚来汽车</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -959,7 +971,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>中场茶歇区 / 体验台</t>
+          <t>中场茶歇区（16:00-16:50）</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1025,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>签到礼品 / 易拉宝</t>
+          <t>签到礼品 + 圆桌三 / 闭幕赞助</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1155,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>晚宴冠名背景 KT 板</t>
+          <t>【绿城·潮鸣】晚宴冠名背景 KT 板 + 邀请码核验物料</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1178,7 +1190,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>主视觉一致性</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1205,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>晚宴礼品</t>
+          <t>晚宴定制礼品</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待定 / 500 份</t>
+          <t>500 份</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1228,7 +1240,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>凭专属邀请码入场</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1300,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>福布斯中国</t>
+          <t>福布斯中国 AI 评选委员会</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>颁奖物料（奖牌 / 证书）</t>
+          <t>★ 颁奖物料（奖杯 / 证书 / 颁奖背景板）</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1303,7 +1315,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>5/22 12:00 前</t>
+          <t>5/22 12:00 前（必到）</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -1318,7 +1330,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>颁奖区暂存</t>
+          <t>主舞台 + 颁奖区</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1328,7 +1340,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>闭幕颁奖典礼需</t>
+          <t>★ 颁奖典礼 14:25-14:40 启用，不得延误</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1350,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>蔚来汽车</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1478,7 +1490,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>交响乐会期间补水</t>
+          <t>中场前移至 16:00-16:50</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1716,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>本届峰会得以呈现，特别感谢以下合作伙伴：晚宴冠名战略合作伙伴——绿城中国；战略合作伙伴——腾讯云、福布斯中国 AI 评选委；特约赞助商——蔚来、泰隆银行；赞助方——茶活力、美年大健康、复金汇、古井贡酒·年份原浆。让我们再次以掌声致谢。</t>
+          <t>本届峰会得以呈现，特别感谢——晚宴冠名战略合作伙伴 绿城中国；战略合作伙伴 腾讯云、福布斯中国人工智能科技企业评选委员会；特约赞助商 蔚来汽车、泰隆银行；赞助方 茶活力、美年大健康、复金汇、古井贡酒·年份原浆。让我们再次以掌声致谢。</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1716,7 +1728,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>B. 分时段定点口播</t>
+          <t>B. 分时段定点口播（按官方最终定稿议程）</t>
         </is>
       </c>
     </row>
@@ -1728,78 +1740,78 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>圆桌一开始前</t>
+          <t>★ 颁奖典礼·高光启幕</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>感谢战略合作伙伴 腾讯云 对本届 AI 硬核圆桌的鼎力支持，腾讯云正以全栈 AI 能力服务千行百业。</t>
+          <t>感谢战略合作伙伴 福布斯中国人工智能科技企业评选委员会 联合颁布本届年度领军机构。让我们以掌声向所有获奖机构致敬，为全天硬核产业博弈奠定荣誉基调。</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>姚志勇 / 胡继刚</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>巅峰对话开始前</t>
+          <t>圆桌一前</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>接下来的【云端生态与 AI 商业化“天花板”】巅峰对话由 腾讯云 联合呈现，并由福布斯中国共同发布相关评选成果。</t>
+          <t>感谢战略合作伙伴 腾讯云 对本届 AI 硬核圆桌的鼎力支持，腾讯云正以全栈 AI 能力服务千行百业。</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>胡继刚</t>
+          <t>王珏</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>交响乐会开始前</t>
+          <t>圆桌二（巅峰对话）前</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>中场艺术留白由 茶活力 与 美年大健康 共同支持，请各位嘉宾在大厅区品茶、体验健康检测，享受这片刻的舒展。</t>
+          <t>接下来的【从算力引擎到新质资产——AI 全产业链的商业化实战】巅峰对话由 腾讯云 联合呈现。</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>主持人</t>
+          <t>胡继刚</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>主旨演讲 3 前</t>
+          <t>中场交响乐会前</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>感谢特约赞助商 泰隆银行，多年来深耕科技金融，为今日特殊机遇与不良资产投资议题提供专业视角。</t>
+          <t>中场艺术留白由 茶活力 与 美年大健康 共同支持，请各位嘉宾在大厅区品茶、体验健康检测。</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1811,44 +1823,44 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>投资圆桌前</t>
+          <t>主旨 3 前</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>投资大圆桌由 复金汇 战略支持。</t>
+          <t>感谢特约赞助商 泰隆银行，多年来深耕科技金融，为今日特殊机遇与不良资产投资议题提供专业视角。</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>黄欣</t>
+          <t>主持人</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>颁奖典礼</t>
+          <t>圆桌三 + 闭幕仪式前</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>感谢 福布斯中国 AI 评选委 联合颁布本届年度领军机构。+ 开场致谢段重述</t>
+          <t>投资大圆桌由 复金汇 战略支持。本环节同时为本届峰会的闭幕仪式。</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>姚志勇</t>
+          <t>黄欣</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1872,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>晚宴开场</t>
+          <t>【绿城·潮鸣】晚宴开场</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>热烈欢迎各位出席今晚的高端闭门晚宴。本次晚宴由 绿城中国 冠名战略合作支持，古井贡酒·年份原浆 为晚宴用酒，蔚来 为本次峰会出行合作伙伴，请大家共同举杯，致谢。</t>
+          <t>热烈欢迎各位出席【绿城·潮鸣】星耀北外滩——AI 领袖定制晚宴。本次晚宴由 绿城中国 冠名战略合作支持，古井贡酒·年份原浆 为晚宴用酒，蔚来汽车 为出行合作伙伴，请大家共同举杯，致谢。</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1894,7 +1906,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>感谢绿城中国晚宴冠名 / 感谢腾讯云战略合作 / 感谢福布斯中国战略合作 / 感谢蔚来、泰隆银行特约赞助 / 感谢茶活力、美年大健康、复金汇、古井贡酒·年份原浆</t>
+          <t>感谢绿城中国晚宴冠名【绿城·潮鸣】 / 感谢腾讯云战略合作 / 感谢福布斯中国 AI 评选委员会战略合作 / 感谢蔚来汽车、泰隆银行特约赞助 / 感谢茶活力、美年大健康、复金汇、古井贡酒·年份原浆</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1975,7 +1987,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>晚宴背景板 LOGO 全景 + 冠名牌特写；冠名嘉宾入场剪影；嘉宾致辞特写</t>
+          <t>晚宴背景板【绿城·潮鸣】LOGO 全景 + 冠名牌特写；专属邀请码核验入场剪影；嘉宾致辞特写</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -2000,12 +2012,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>主舞台 LOGO 墙特写；徐泳泽演讲 / 圆桌发言镜头 ≥ 6 个；签到处易拉宝</t>
+          <t>主舞台 LOGO 墙特写；徐泳泽圆桌二发言镜头 ≥ 6 个；签到处易拉宝</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>13:00 / 15:05-15:45 / 闭幕</t>
+          <t>13:00 / 15:20-16:00 圆桌二 / 闭幕</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2020,22 +2032,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>福布斯中国</t>
+          <t>福布斯中国 AI 评选委员会</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>颁奖典礼奖杯 / 证书特写；颁奖瞬间合影</t>
+          <t>★ 颁奖典礼奖杯 / 证书特写；颁奖瞬间合影；获奖代表镜头</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>18:15 颁奖</t>
+          <t>★ 14:25-14:40 颁奖典礼（移至上半场）</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>颁奖合影 ≥ 3 张 + 奖杯特写</t>
+          <t>颁奖合影 ≥ 5 张 + 奖杯特写 + 1 分钟视频</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2057,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>蔚来汽车</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2055,7 +2067,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>13:00 / 中场 15:45</t>
+          <t>13:00 / 中场 16:00</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -2105,7 +2117,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>15:45-16:35 中场</t>
+          <t>16:00-16:50 中场（前移）</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -2150,17 +2162,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>签到礼品台特写 + 嘉宾领取瞬间；袁一栋合伙人镜头</t>
+          <t>签到礼品台特写 + 嘉宾领取瞬间；袁一栋合伙人镜头；圆桌三发言镜头</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>签到 13:00-13:30</t>
+          <t>签到 13:00-13:30 / 17:50-18:30 圆桌三+闭幕</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>实拍 ≥ 4 张</t>
+          <t>实拍 ≥ 6 张</t>
         </is>
       </c>
     </row>
@@ -2200,12 +2212,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>闭幕大合影 + LOGO 墙合影</t>
+          <t>闭幕大合影（圆桌三结束后）+ LOGO 墙合影</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:30 闭幕大合影</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -2228,7 +2240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2268,7 +2280,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>赞助商口播文案、对接人、物资清单回收截止</t>
+          <t>赞助商口播文案、对接人、物资清单回收；福布斯获奖名单/颁奖嘉宾确认；绿城晚宴邀请码机制确认</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2319,7 +2331,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>蔚来展车（如有）到场</t>
+          <t>蔚来汽车展车（如有）到场</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2370,7 +2382,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>台卡、主席台陈列就位 / 福布斯颁奖物料到位</t>
+          <t>台卡、主席台陈列就位 / ★ 福布斯颁奖物料必到</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2433,32 +2445,49 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>5/22 16:30</t>
+          <t>5/22 14:25-14:40</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>晚宴桌引位牌布置</t>
+          <t>★ 第四届颁奖典礼（高光启幕）</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>A 组 / E 组</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>5/22 16:30</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>晚宴桌引位牌布置</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>A 组 / E 组</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>5/22 18:30</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>闭门晚宴开始</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>【绿城·潮鸣】星耀北外滩——AI 领袖定制晚宴 开始</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2524,7 +2553,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>嘉宾签到与入场</t>
+          <t>嘉宾签到与入场（凭邀请码核验、展区互动与高端资源对接）</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2551,12 +2580,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>姚志勇</t>
+          <t>姚志勇 教授</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>复旦管院教授、北大经院上海校友会会长</t>
+          <t>复旦大学管理学院 / 北京大学经济学院上海校友会会长</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2607,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>恒生研究院院长、前上交所总工程师</t>
+          <t>恒生电子研究院院长、前上海证券交易所总工程师</t>
         </is>
       </c>
     </row>
@@ -2607,39 +2636,39 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>14:25-15:05</t>
+          <t>14:25-14:40</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>圆桌论坛一 · AI 硬核圆桌——技术突围与新质生产力落地</t>
+          <t>★ 第四届 2026 人工智能商业化落地颁奖典礼（高光启幕）</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>主持：王珏；嘉宾：白硕、李龙、齐宝鑫、刘文平</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>总结年度成果，表彰行业领军机构</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>15:05-15:45</t>
+          <t>14:40-15:20</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>巅峰对话 · 云端生态与 AI 商业化“天花板”</t>
+          <t>圆桌论坛一 · AI 硬核圆桌——技术突围与新质生产力落地</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>主持：胡继刚；嘉宾：刘帅华、徐泳泽、黎远、刘剑英、于敬</t>
+          <t>主持：王珏；嘉宾：白硕、李龙、齐宝鑫、刘文平</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -2651,132 +2680,132 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>15:45-16:35</t>
+          <t>15:20-16:00</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>陆家嘴交响乐团·时光音乐会</t>
+          <t>圆桌论坛二 · 巅峰对话——从算力引擎到新质资产（AI 全产业链商业化实战）</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>主持：胡继刚；嘉宾：刘帅华、徐泳泽、黎远、刘剑英、于敬</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>中场艺术留白 + 高净值嘉宾深度社交</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>16:35-16:55</t>
+          <t>16:00-16:50</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>主旨演讲 3 ——《十五五规划之下，特殊机遇/不良资产投资的新机遇》</t>
+          <t>陆家嘴交响乐团·时光音乐会</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>王维军</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>泓塬资产董事长兼总经理</t>
+          <t>中场艺术留白 + 高净值嘉宾深度社交</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>16:55-17:15</t>
+          <t>16:50-17:10</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>主旨演讲 4 ——《从自然利率下降到 K 型经济》</t>
+          <t>主旨演讲 3 ——《十五五规划之下，特殊机遇/不良资产投资的新机遇》</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>寇文红</t>
+          <t>王维军</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>《跨越自然利率陷阱》作者</t>
+          <t>泓塬资产管理有限公司董事长兼总经理</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>17:15-17:35</t>
+          <t>17:10-17:30</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>主旨演讲 5 ——《从致用之学到量子智能》</t>
+          <t>主旨演讲 4 ——《从自然利率下降到 K 型经济》</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>张露瑶 博士</t>
+          <t>寇文红</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>昆山杜克大学助理教授</t>
+          <t>《跨越自然利率陷阱》作者</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>17:35-18:15</t>
+          <t>17:30-17:50</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>圆桌论坛二 · 投资大圆桌——寻找新质资产风口</t>
+          <t>主旨演讲 5 ——《从致用之学到量子智能》</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>主持：黄欣；嘉宾：曲承东、刘胜利、饶雪莹、马俊杰</t>
+          <t>张露瑶 博士</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>昆山杜克大学助理教授（北大经院 2008 级）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>18:15-18:30</t>
+          <t>17:50-18:30</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>第四届 2026 人工智能商业化落地颁奖典礼暨闭幕仪式</t>
+          <t>圆桌论坛三 · 投资大圆桌——寻找新质资产风口与闭幕仪式</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>主持：黄欣；嘉宾：曲承东、刘胜利、饶雪莹、马俊杰</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>总结全天成果，表彰年度领军机构</t>
+          <t>圆桌 + 闭幕合并</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2817,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>VIP 高端闭门晚宴</t>
+          <t>【绿城·潮鸣】星耀北外滩——AI 领袖定制晚宴</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2798,7 +2827,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>500 人高端圈层社交与项目对接（冠名：绿城中国）</t>
+          <t>定向邀约制（凭专属邀请码入场） / 500 人高端私密社交</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3104,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>三、圆桌一 · AI 硬核圆桌（蓝色 ●）</t>
+          <t>三、圆桌论坛一 · AI 硬核圆桌（14:40-15:20，蓝色 ●）</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3271,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>四、巅峰对话 · 云端生态与 AI 商业化（蓝色 ●）</t>
+          <t>四、圆桌论坛二 · 巅峰对话——从算力引擎到新质资产（15:20-16:00，蓝色 ●）</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3357,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>东区渠道总经理</t>
+          <t>华东区渠道总经理</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -3441,7 +3470,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>五、圆桌二 · 投资大圆桌（蓝色 ●）</t>
+          <t>五、圆桌论坛三 · 投资大圆桌——寻找新质资产风口与闭幕仪式（17:50-18:30，蓝色 ●）</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3922,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>东区渠道总经理</t>
+          <t>华东区渠道总经理</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -8977,7 +9006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9030,12 +9059,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>姚志勇</t>
+          <t>姚志勇 教授</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>复旦管院 / 北大经院上海校友会</t>
+          <t>复旦大学管理学院 / 北京大学经济学院上海校友会</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -9064,12 +9093,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>恒生研究院</t>
+          <t>恒生电子研究院</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>院长</t>
+          <t>院长、前上海证券交易所总工程师</t>
         </is>
       </c>
     </row>
@@ -9105,124 +9134,124 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>四、圆桌论坛一（14:25-15:05）</t>
+          <t>四、★ 颁奖典礼·高光启幕（14:25-14:40）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>主持位</t>
+          <t>主礼嘉宾 1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>姚志勇 教授</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>北大经院上海校友会</t>
+          <t>复旦管院 / 北大经院上海校友会</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>理事</t>
+          <t>教授 / 会长</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>嘉宾位 1</t>
+          <t>主礼嘉宾 2</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>白硕</t>
+          <t>胡继刚</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>恒生研究院</t>
+          <t>复旦住房政策研究中心 / 杨浦科企联</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>院长、首席科学家</t>
+          <t>秘书长 / 执行会长</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>嘉宾位 2</t>
+          <t>主礼嘉宾 3</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>李龙</t>
+          <t>黄欣</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>龙旗科技</t>
+          <t>国联安基金 / 北大经院上海校友会</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>机器人业务部总经理、思行 AI 联合创始人</t>
+          <t>秘书长</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>嘉宾位 3</t>
+          <t>主礼嘉宾 4</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>齐宝鑫</t>
+          <t>福布斯中国-代表</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>上海市锦天城律师事务所</t>
+          <t>福布斯中国 AI 评选委员会</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>高级合伙人</t>
+          <t>待补</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>嘉宾位 4</t>
+          <t>主礼嘉宾 5</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>刘文平</t>
+          <t>绿城中国-代表</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>绿城中国</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>能源专家、原上市公司董事长</t>
+          <t>待补</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>五、巅峰对话（15:05-15:45）</t>
+          <t>五、圆桌论坛一 · AI 硬核圆桌（14:40-15:20）</t>
         </is>
       </c>
     </row>
@@ -9234,17 +9263,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>胡继刚</t>
+          <t>王珏</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>复旦住房政策研究中心 / 杨浦科企联</t>
+          <t>北京大学经济学院上海校友会</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>秘书长 / 执行会长</t>
+          <t>理事</t>
         </is>
       </c>
     </row>
@@ -9256,17 +9285,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>刘帅华</t>
+          <t>白硕</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>火山引擎</t>
+          <t>恒生电子研究院</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>上海央国企业务负责人</t>
+          <t>院长、首席科学家</t>
         </is>
       </c>
     </row>
@@ -9278,17 +9307,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>徐泳泽</t>
+          <t>李龙</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>腾讯云</t>
+          <t>龙旗科技</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>产业生态合作部东区渠道总经理</t>
+          <t>机器人业务部总经理、思行 AI 联合创始人</t>
         </is>
       </c>
     </row>
@@ -9300,17 +9329,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>黎远</t>
+          <t>齐宝鑫</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>福世合仑信息科技</t>
+          <t>上海市锦天城律师事务所</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>副总裁</t>
+          <t>高级合伙人</t>
         </is>
       </c>
     </row>
@@ -9322,338 +9351,360 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>刘剑英</t>
+          <t>刘文平</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>仪电智算</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>商务生态总监</t>
+          <t>能源专家、原上市公司董事长</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>嘉宾位 5</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>于敬</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>达观数据</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>联合创始人</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>六、圆桌论坛二 · 巅峰对话（15:20-16:00）</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>六、主旨演讲 3（16:35-16:55）</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>主持位</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>胡继刚</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>复旦住房政策研究中心 / 杨浦科企联</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>秘书长 / 执行会长</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>演讲台</t>
+          <t>嘉宾位 1</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>王维军</t>
+          <t>刘帅华</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>泓塬资产</t>
+          <t>火山引擎</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>董事长兼总经理</t>
+          <t>上海央国企业务负责人</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>七、主旨演讲 4（16:55-17:15）</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>嘉宾位 2</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>徐泳泽</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>腾讯云</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>产业生态合作部华东区渠道总经理</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>演讲台</t>
+          <t>嘉宾位 3</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>寇文红</t>
+          <t>黎远</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>《跨越自然利率陷阱》作者</t>
+          <t>福世合仑信息科技</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>副总裁</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>八、主旨演讲 5（17:15-17:35）</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>嘉宾位 4</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>刘剑英</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>上海仪电智算科技</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>商务生态总监</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>演讲台</t>
+          <t>嘉宾位 5</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>张露瑶 博士</t>
+          <t>于敬</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>昆山杜克大学 / 北大经院 08 级</t>
+          <t>达观数据</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>助理教授</t>
+          <t>联合创始人</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>九、圆桌论坛二（17:35-18:15）</t>
+          <t>七、主旨演讲 3（16:50-17:10）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>主持位</t>
+          <t>演讲台</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>黄欣</t>
+          <t>王维军</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>国联安基金 / 北大经院上海校友会</t>
+          <t>泓塬资产管理有限公司</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>量化投资部董事 / 秘书长</t>
+          <t>董事长兼总经理</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>嘉宾位 1</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>曲承东</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>招商银行资金运营中心</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>总助</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>八、主旨演讲 4（17:10-17:30）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>嘉宾位 2</t>
+          <t>演讲台</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>刘胜利</t>
+          <t>寇文红</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>长江证券</t>
+          <t>《跨越自然利率陷阱》作者</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>金融工程首席分析师</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>嘉宾位 3</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>饶雪莹</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>金浦投资</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>合伙人</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>九、主旨演讲 5（17:30-17:50）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>嘉宾位 4</t>
+          <t>演讲台</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>马俊杰</t>
+          <t>张露瑶 博士</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>小马创业村 / 铂泉投资</t>
+          <t>昆山杜克大学 / 北大经院 2008 级</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>董事长</t>
+          <t>助理教授</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>十、颁奖典礼暨闭幕仪式（18:15-18:30）</t>
+          <t>十、圆桌论坛三 · 投资大圆桌+闭幕仪式（17:50-18:30）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>颁奖嘉宾 1</t>
+          <t>主持位</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>姚志勇</t>
+          <t>黄欣</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>复旦管院 / 北大经院上海校友会</t>
+          <t>国联安基金 / 北大经院上海校友会</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>教授 / 会长</t>
+          <t>量化投资部董事 / 秘书长</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>颁奖嘉宾 2</t>
+          <t>嘉宾位 1</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>胡继刚</t>
+          <t>曲承东</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>杨浦科企联</t>
+          <t>招商银行资金运营中心</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>执行会长</t>
+          <t>总经理助理</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>颁奖嘉宾 3</t>
+          <t>嘉宾位 2</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>黄欣</t>
+          <t>刘胜利</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>北大经院上海校友会</t>
+          <t>长江证券</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>秘书长</t>
+          <t>金融工程首席分析师</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>颁奖嘉宾 4</t>
+          <t>嘉宾位 3</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>绿城中国-代表</t>
+          <t>饶雪莹</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>绿城中国</t>
+          <t>金浦投资 / 北大金融校友联合会</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>合伙人 / 副会长</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>嘉宾位 4</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>马俊杰</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>小马创业村 / 铂泉投资</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>董事长</t>
         </is>
       </c>
     </row>
@@ -9662,14 +9713,14 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A30:D30"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A24:D24"/>
     <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/5月22日峰会/导出文件/2026峰会会务名单.xlsx
+++ b/5月22日峰会/导出文件/2026峰会会务名单.xlsx
@@ -21,6 +21,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赞助商口播" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摄影特写" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键时间节点" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="颁奖典礼推荐" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="颁奖推荐组合" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物资摆放顺序图" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,7 +580,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>复旦大学未来信息创新学院、上海市云计算创新基地、上海市杨浦区科技企业联合会、上海市虹口区科技企业联合会、中国商业文化研究会长三角分会、东投资联盟、红瓦（陆家嘴）共创中心</t>
+          <t>复旦大学未来信息创新学院、上海市云计算创新基地、上海市杨浦区科技企业联合会、上海市虹口区科技企业联合会、中国商业文化研究会长三角分会、中东投资联盟、红瓦（陆家嘴）共创中心</t>
         </is>
       </c>
     </row>
@@ -589,7 +592,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>腾讯云、福布斯中国人工智能科技企业评选委员会</t>
+          <t>腾讯云（福布斯中国 AI 评选委员会已退出）</t>
         </is>
       </c>
     </row>
@@ -613,7 +616,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>【绿城·潮鸣】星耀北外滩——AI 领袖定制晚宴（凭专属邀请码入场）</t>
+          <t>【绿城·潮鸣】星耀北外滩——AI 领袖定制晚宴（凭专属邀请码入场，每桌 12 人，绿城每桌 1 人）</t>
         </is>
       </c>
     </row>
@@ -625,7 +628,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>蔚来汽车、泰隆银行</t>
+          <t>蔚来汽车（不展车）、华为鸿蒙汽车（新增 · 展车）、泰隆银行</t>
         </is>
       </c>
     </row>
@@ -637,7 +640,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>茶活力、美年大健康、复金汇、古井贡酒·年份原浆</t>
+          <t>茶活力（孟高举）、美年大健康（鲁菲菲）、复金汇（袁一栋）、古井贡酒·年份原浆（李旭欢）</t>
         </is>
       </c>
     </row>
@@ -673,7 +676,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>王珏 13817642219</t>
+          <t>王胜 13083003003</t>
         </is>
       </c>
     </row>
@@ -685,19 +688,19 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>黄欣（北京大学经济学院上海校友会秘书长）</t>
+          <t>韦佳玉 17301836967</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>整体校对</t>
+          <t>会务统筹</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>安淑娟 13661612711</t>
+          <t>陈潇 Kelly 15021307893</t>
         </is>
       </c>
     </row>
@@ -715,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -772,17 +775,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>缪川 / 笪浩</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>待补</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>晚宴冠名【绿城·潮鸣】/ 邀请码核验 / 礼品 / 背景板</t>
+          <t>晚宴冠名【绿城·潮鸣】/ 品宣产品 + 定制礼品 / 每桌 1 人 ×42 桌</t>
         </is>
       </c>
     </row>
@@ -804,39 +807,39 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>（现场出席）</t>
+          <t>现场出席</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>华东区渠道总经理 / 战略合作 / 圆桌二嘉宾</t>
+          <t>华东区渠道总经理 / 圆桌二嘉宾</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>战略合作伙伴</t>
+          <t>特约赞助商</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>福布斯中国人工智能科技企业评选委员会</t>
+          <t>蔚来汽车</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>李睿</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>待补</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>★ 颁奖典礼物料（14:25-14:40 启用）</t>
+          <t>易拉宝 + 礼品（不展车）</t>
         </is>
       </c>
     </row>
@@ -848,7 +851,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>蔚来汽车</t>
+          <t>华为鸿蒙汽车（新增 ★）</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -863,7 +866,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>出行合作 / 试驾展车 / 礼品</t>
+          <t>★ 展车 + 易拉宝 + 礼品</t>
         </is>
       </c>
     </row>
@@ -875,22 +878,22 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>泰隆银行 上海分行</t>
+          <t>泰隆银行 虹口支行</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>杨红江</t>
+          <t>林骁</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>（现场出席）</t>
+          <t>13058861308</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>支行合作</t>
+          <t>晚宴整桌（T05，已取消杨红江/汤梦薇）</t>
         </is>
       </c>
     </row>
@@ -902,49 +905,49 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>泰隆银行 虹口支行</t>
+          <t>泰隆银行 杨浦支行</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>林骁</t>
+          <t>陈煜</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>13058861308</t>
+          <t>13671896951</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>晚宴整桌（T05）</t>
+          <t>晚宴整桌（T06）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>特约赞助商</t>
+          <t>赞助方</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>泰隆银行 杨浦支行</t>
+          <t>茶活力</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>陈煜</t>
+          <t>孟高举</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>13671896951</t>
+          <t>待补</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>晚宴整桌（T06）</t>
+          <t>中场茶歇区（16:00-16:50）</t>
         </is>
       </c>
     </row>
@@ -956,22 +959,22 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>茶活力</t>
+          <t>美年大健康</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>鲁菲菲</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>待补</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
-        </is>
-      </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>中场茶歇区（16:00-16:50）</t>
+          <t>大厅健康检测体验台</t>
         </is>
       </c>
     </row>
@@ -983,22 +986,22 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>美年大健康</t>
+          <t>复金汇</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>袁一栋</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>15995991077</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>大厅健康检测体验台</t>
+          <t>签到礼品 + 圆桌三 / 闭幕赞助</t>
         </is>
       </c>
     </row>
@@ -1010,55 +1013,63 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>复金汇</t>
+          <t>古井贡酒·年份原浆</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>袁一栋</t>
+          <t>李旭欢</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>15995991077</t>
+          <t>待补</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>签到礼品 + 圆桌三 / 闭幕赞助</t>
+          <t>晚宴用酒 2 瓶 × 10 桌 = 20 瓶 + 礼盒</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>赞助方</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>古井贡酒·年份原浆</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>晚宴用酒 / 品鉴礼盒</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>已退出（不再参与本次峰会赞助与颁奖）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>福布斯中国人工智能科技企业评选委员会</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>★ 已退出，颁奖典礼由组委会主办（无福布斯 LOGO）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1155,32 +1166,32 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>【绿城·潮鸣】晚宴冠名背景 KT 板 + 邀请码核验物料</t>
+          <t>品宣产品（KT 板 / 易拉宝 / 宣传册）</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>1 套</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5/22 09:00 前</t>
+          <t>5/22 09:00-10:00</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>缪川 / 笪浩</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>待补</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
-        </is>
-      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>晚宴主入口</t>
+          <t>晚宴主入口 + 主舞台</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -1205,7 +1216,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>晚宴定制礼品</t>
+          <t>定制礼品</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1215,19 +1226,19 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>5/22 14:00 前</t>
+          <t>5/22 09:00-11:00</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>缪川 / 笪浩</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>待补</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
-        </is>
-      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>晚宴每席</t>
@@ -1240,7 +1251,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>凭专属邀请码入场</t>
+          <t>每桌 1 位绿城代表</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1266,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>易拉宝 / 礼品</t>
+          <t>易拉宝 + 礼品</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1265,7 +1276,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5/22 10:00 前</t>
+          <t>5/22 09:00-11:00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1275,12 +1286,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>现场出席</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>主舞台两侧 / 签到处</t>
+          <t>主舞台两侧 + 签到处</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -1300,22 +1311,22 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>福布斯中国 AI 评选委员会</t>
+          <t>华为鸿蒙汽车（新增 ★）</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>★ 颁奖物料（奖杯 / 证书 / 颁奖背景板）</t>
+          <t>★ 展车 + 易拉宝 + 礼品</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>待定 / 若干</t>
+          <t>1 车 + 物料</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>5/22 12:00 前（必到）</t>
+          <t>5/22 09:00-10:00</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -1330,17 +1341,17 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>主舞台 + 颁奖区</t>
+          <t>一滴水入口外</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>张蒙</t>
+          <t>葛九明、李正超</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>★ 颁奖典礼 14:25-14:40 启用，不得延误</t>
+          <t>提前确认场地通行证</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1366,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>试驾展车 / 易拉宝 / 礼品</t>
+          <t>易拉宝 + 礼品（不展车）</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1365,32 +1376,32 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>5/22 08:00（展车）/ 10:00（其他）</t>
+          <t>5/22 09:00-11:00</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
+          <t>李睿</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
           <t>待补</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
-        </is>
-      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>一滴水入口外 / 大厅</t>
+          <t>大厅展位</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>葛九明、李正超</t>
+          <t>葛九明</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>提前确认场地通行证</t>
+          <t>不展示车</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1416,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>易拉宝 / 礼品 / 客户伴手礼</t>
+          <t>易拉宝 + 礼品 + 客户伴手礼</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1415,7 +1426,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>5/22 10:00 前</t>
+          <t>5/22 09:00-11:00</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1460,24 +1471,24 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>1 套</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>5/22 09:00 前</t>
+          <t>5/22 09:00-11:00</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
+          <t>孟高举</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
           <t>待补</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
-        </is>
-      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>中场茶歇区</t>
@@ -1490,7 +1501,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>中场前移至 16:00-16:50</t>
+          <t>中场 16:00-16:50</t>
         </is>
       </c>
     </row>
@@ -1510,17 +1521,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>1 套</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>5/22 09:00 前</t>
+          <t>5/22 09:00-11:00</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>鲁菲菲</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1565,7 +1576,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>5/22 10:00 前</t>
+          <t>5/22 09:00-11:00</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1590,7 +1601,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1610,27 +1621,27 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>50 桌×2 瓶 + 礼盒若干</t>
+          <t>2 瓶 × 10 桌 = 20 瓶 + 礼盒</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>5/22 14:00 前</t>
+          <t>5/22 09:00-11:00</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
+          <t>李旭欢</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
           <t>待补</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
-        </is>
-      </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>晚宴每桌</t>
+          <t>晚宴 T01-T10 桌</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1640,7 +1651,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>提前与场地报备酒水</t>
+          <t>需提前与场地报备酒水</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1727,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>本届峰会得以呈现，特别感谢——晚宴冠名战略合作伙伴 绿城中国；战略合作伙伴 腾讯云、福布斯中国人工智能科技企业评选委员会；特约赞助商 蔚来汽车、泰隆银行；赞助方 茶活力、美年大健康、复金汇、古井贡酒·年份原浆。让我们再次以掌声致谢。</t>
+          <t>本届峰会得以呈现，特别感谢——晚宴冠名战略合作伙伴 绿城中国；战略合作伙伴 腾讯云；特约赞助商 蔚来汽车、华为鸿蒙汽车、泰隆银行；赞助方 茶活力、美年大健康、复金汇、古井贡酒·年份原浆。让我们再次以掌声致谢。</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1745,7 +1756,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>感谢战略合作伙伴 福布斯中国人工智能科技企业评选委员会 联合颁布本届年度领军机构。让我们以掌声向所有获奖机构致敬，为全天硬核产业博弈奠定荣誉基调。</t>
+          <t>本届颁奖典礼共同表彰本年度行业领军机构，为全天硬核产业博弈奠定荣誉基调。让我们以掌声向所有获奖机构致敬。</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1767,7 +1778,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>感谢战略合作伙伴 腾讯云 对本届 AI 硬核圆桌的鼎力支持，腾讯云正以全栈 AI 能力服务千行百业。</t>
+          <t>感谢战略合作伙伴 腾讯云 对本届 AI 硬核圆桌的鼎力支持。</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1811,7 +1822,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>中场艺术留白由 茶活力 与 美年大健康 共同支持，请各位嘉宾在大厅区品茶、体验健康检测。</t>
+          <t>中场艺术留白由 茶活力 与 美年大健康 共同支持。</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1833,7 +1844,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>感谢特约赞助商 泰隆银行，多年来深耕科技金融，为今日特殊机遇与不良资产投资议题提供专业视角。</t>
+          <t>感谢特约赞助商 泰隆银行 深耕科技金融；感谢 蔚来汽车 与 华为鸿蒙汽车，华为鸿蒙汽车展车在一滴水入口外亮相，欢迎嘉宾中场体验。</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1877,7 +1888,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>热烈欢迎各位出席【绿城·潮鸣】星耀北外滩——AI 领袖定制晚宴。本次晚宴由 绿城中国 冠名战略合作支持，古井贡酒·年份原浆 为晚宴用酒，蔚来汽车 为出行合作伙伴，请大家共同举杯，致谢。</t>
+          <t>热烈欢迎各位出席【绿城·潮鸣】星耀北外滩——AI 领袖定制晚宴。本次晚宴由 绿城中国 冠名，古井贡酒·年份原浆 为晚宴用酒，蔚来汽车 与 华为鸿蒙汽车 为出行合作伙伴。</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1906,7 +1917,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>感谢绿城中国晚宴冠名【绿城·潮鸣】 / 感谢腾讯云战略合作 / 感谢福布斯中国 AI 评选委员会战略合作 / 感谢蔚来汽车、泰隆银行特约赞助 / 感谢茶活力、美年大健康、复金汇、古井贡酒·年份原浆</t>
+          <t>感谢绿城中国晚宴冠名【绿城·潮鸣】 / 感谢腾讯云战略合作 / 感谢蔚来汽车、华为鸿蒙汽车、泰隆银行特约赞助 / 感谢茶活力、美年大健康、复金汇、古井贡酒·年份原浆</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1987,17 +1998,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>晚宴背景板【绿城·潮鸣】LOGO 全景 + 冠名牌特写；专属邀请码核验入场剪影；嘉宾致辞特写</t>
+          <t>【绿城·潮鸣】LOGO 全景 + 冠名牌；邀请码核验入场剪影；缪川/笪浩 致辞</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>18:00 晚宴布置 / 18:30 入场 / 致辞</t>
+          <t>18:00 / 18:30 / 致辞</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>横版 / 竖版各 5 张 + 视频 30 秒</t>
+          <t>横竖各 5 + 视频 30 秒</t>
         </is>
       </c>
     </row>
@@ -2012,17 +2023,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>主舞台 LOGO 墙特写；徐泳泽圆桌二发言镜头 ≥ 6 个；签到处易拉宝</t>
+          <t>主舞台 LOGO 墙；徐泳泽圆桌二发言 ≥6 个</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>13:00 / 15:20-16:00 圆桌二 / 闭幕</t>
+          <t>13:00 / 15:20-16:00 / 闭幕</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>嘉宾特写 6 张 + 物料特写 4 张</t>
+          <t>嘉宾 6 + 物料 4</t>
         </is>
       </c>
     </row>
@@ -2032,22 +2043,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>福布斯中国 AI 评选委员会</t>
+          <t>★ 华为鸿蒙汽车（新增）</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>★ 颁奖典礼奖杯 / 证书特写；颁奖瞬间合影；获奖代表镜头</t>
+          <t>★ 展车 360° 全景 + 内饰 + 车标 LOGO；嘉宾试车</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>★ 14:25-14:40 颁奖典礼（移至上半场）</t>
+          <t>09:00 展车到位 + 全天 + 中场 16:00</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>颁奖合影 ≥ 5 张 + 奖杯特写 + 1 分钟视频</t>
+          <t>展车 ≥10 + 互动 ≥6 + 视频 30 秒</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2073,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>入口展车全景 + 内饰 + 嘉宾驻足；易拉宝特写</t>
+          <t>大厅易拉宝 + 礼品 + 嘉宾领取；李睿镜头</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -2072,7 +2083,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>展车 ≥ 8 张 + 嘉宾互动 4 张</t>
+          <t>实拍 ≥6</t>
         </is>
       </c>
     </row>
@@ -2112,17 +2123,17 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>中场茶歇区嘉宾品茶画面；体验台特写</t>
+          <t>中场茶歇区 + 孟高举镜头</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>16:00-16:50 中场（前移）</t>
+          <t>16:00-16:50 中场</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>实拍 ≥ 6 张 + 短视频 15 秒</t>
+          <t>≥6 + 短视频 15s</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2148,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>健康检测体验台 + 嘉宾参与；易拉宝</t>
+          <t>健康检测 + 鲁菲菲镜头</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -2147,7 +2158,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>实拍 ≥ 6 张</t>
+          <t>≥6</t>
         </is>
       </c>
     </row>
@@ -2162,17 +2173,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>签到礼品台特写 + 嘉宾领取瞬间；袁一栋合伙人镜头；圆桌三发言镜头</t>
+          <t>签到礼品台 + 袁一栋 + 圆桌三发言</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>签到 13:00-13:30 / 17:50-18:30 圆桌三+闭幕</t>
+          <t>13:00 / 17:50-18:30</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>实拍 ≥ 6 张</t>
+          <t>≥6</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2198,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>晚宴餐桌酒瓶特写 + 嘉宾举杯合影；致敬环节</t>
+          <t>T01-T10 餐桌酒瓶 + 举杯合影；李旭欢镜头</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -2197,7 +2208,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>实拍 ≥ 8 张</t>
+          <t>≥10</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2251,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2280,12 +2291,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>赞助商口播文案、对接人、物资清单回收；福布斯获奖名单/颁奖嘉宾确认；绿城晚宴邀请码机制确认</t>
+          <t>赞助商口播文案 / 对接人 / 物资清单回收；颁奖嘉宾确认；绿城晚宴邀请码机制确认</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>胡继刚 / 王珏</t>
+          <t>胡继刚 / 王珏 / 陈潇</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2308,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>圆桌桌号牌、圆桌大卡、席卡、胸卡完成印刷</t>
+          <t>圆桌桌号牌、圆桌大卡、席卡（每桌 12 人）、胸卡 完成印刷</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2314,180 +2325,129 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>T11-T50 晚宴桌名单最终确认</t>
+          <t>T11-T42 晚宴桌名单最终确认（每桌 12 人，绿城每桌 1 位代表）</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>王珏 / 黄欣 / 安淑娟</t>
+          <t>王珏 / 陈潇 / 安淑娟</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>5/22 08:00</t>
+          <t>★ 5/22 09:00-11:00</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>蔚来汽车展车（如有）到场</t>
+          <t>★ 所有赞助方物资统一到场签收 / 上架 / 按摆放顺序图就位（含华为鸿蒙汽车展车 09:00-10:00 必到）</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>葛九明 / 李正超（D 组）</t>
+          <t>D 组（葛九明、李正超）+ G 组</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>5/22 09:00</t>
+          <t>5/22 12:00</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>绿城背景板、茶活力、美年大健康 物资到场</t>
+          <t>台卡、主席台陈列就位（无福布斯物料）</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>D 组 / G 组</t>
+          <t>B 组 / 张蒙</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>5/22 10:00</t>
+          <t>5/22 13:00-13:30</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>腾讯云、泰隆、复金汇 物资到场</t>
+          <t>嘉宾签到与入场</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>D 组 / G 组</t>
+          <t>A 组（韦佳玉、李振春）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>5/22 12:00</t>
+          <t>5/22 13:30</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>台卡、主席台陈列就位 / ★ 福布斯颁奖物料必到</t>
+          <t>峰会开幕（姚志勇 致辞）</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>B 组 / 张蒙</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>5/22 13:00-13:30</t>
+          <t>★ 5/22 14:25-14:40</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>嘉宾签到与入场</t>
+          <t>★ 第四届颁奖典礼（高光启幕，黄欣不参加 / 福布斯不参与）</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>A 组（韦佳玉、李政春）</t>
+          <t>姚志勇 + 胡继刚 + 9 位颁奖嘉宾</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>5/22 13:30</t>
+          <t>5/22 16:30</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>峰会开幕（姚志勇 致辞）</t>
+          <t>晚宴桌引位牌布置</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A 组 / E 组</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>5/22 14:00</t>
+          <t>5/22 18:30</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>晚宴礼品、古井贡酒到场</t>
+          <t>【绿城·潮鸣】星耀北外滩——AI 领袖定制晚宴 开始（每桌 12 人）</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>F 组 / G 组</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>5/22 14:25-14:40</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>★ 第四届颁奖典礼（高光启幕）</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>5/22 16:30</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>晚宴桌引位牌布置</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>A 组 / E 组</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>5/22 18:30</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>【绿城·潮鸣】星耀北外滩——AI 领袖定制晚宴 开始</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2496,6 +2456,1596 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>★ 颁奖典礼推荐名单（14:25-14:40，黄欣不参加 / 福布斯不参与）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>职务</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>主礼 / 主持（建议 2 位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>主礼致辞</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>姚志勇 教授</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>复旦管院 / 北大经院上海校友会</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>教授 / 会长</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>致辞中嵌入颁奖意图</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>颁奖主持</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>胡继刚</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>复旦住房政策研究中心 / 杨浦科企联</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>秘书长 / 执行会长</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>主控全场节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>A. 战略合作伙伴 / 冠名方（优先级最高）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>缪川 / 笪浩</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>绿城中国</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>冠名方代表</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>晚宴冠名战略合作伙伴</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>徐泳泽</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>腾讯云</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>华东区渠道总经理</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>战略合作伙伴 / 巅峰对话嘉宾</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>B. 特约赞助商</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>李睿</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>蔚来汽车</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>对接人</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>特约赞助商</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>待补</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>华为鸿蒙汽车</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>对接人</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>特约赞助商（新增 ★）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>林骁</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>泰隆银行虹口支行</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>支行行长</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>特约赞助商</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>陈煜</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>泰隆银行杨浦支行</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>支行行长</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>特约赞助商</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>C. 赞助方</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>孟高举</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>茶活力</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>对接人</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>赞助方</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>鲁菲菲</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>美年大健康</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>对接人</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>赞助方</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>袁一栋</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>复金汇</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>合伙人 / 15995991077</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>赞助方</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>李旭欢</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>古井贡酒·年份原浆</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>对接人</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>赞助方</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>D. 协办单位代表</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>高歆</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>上海市云计算创新基地</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>副总经理</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>协办单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>顾炯亮</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>上海市云计算创新基地</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>顾问</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>协办单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>待补</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>上海市虹口区科技企业联合会</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>协办单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>夏洁（如出席）</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>虹口区科企联</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>秘书长</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>协办单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>待补</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>上海市杨浦区科技企业联合会</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>协办单位（执行会长由胡继刚兼）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>待补</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>复旦大学未来信息创新学院</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>协办单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>待补</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>中国商业文化研究会长三角分会</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>协办单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>待补</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>中东投资联盟（原写'东投资联盟'）</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>协办单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>待补</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>红瓦（陆家嘴）共创中心</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>协办单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>E. 在场重磅嘉宾（颁奖嘉宾或受奖代表合影）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>白硕</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>恒生电子研究院</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>院长</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>主旨 1，业界顶级</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>夏春 博士</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>香港国际金融学会</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>副会长</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>主旨 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>王维军</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>泓塬资产</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>董事长</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>主旨 3 + 出席理事</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>寇文红</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>《跨越自然利率陷阱》作者</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>主旨 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>张露瑶 博士</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>昆山杜克大学</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>助理教授</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>主旨 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>王珏</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>北大经院上海校友会</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>理事</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>圆桌一主持</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>黎远</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>福世合仑信息科技</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>副总裁</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>圆桌二嘉宾</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>于敬</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>达观数据</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>联合创始人</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>圆桌二嘉宾</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>E9</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>齐宝鑫</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>锦天城律师事务所</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>高级合伙人</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>圆桌一嘉宾</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>李龙</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>龙旗科技</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>机器人业务部总经理</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>圆桌一嘉宾</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>★ 颁奖推荐组合（6 奖项 × 2 颁奖嘉宾 = 12 人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>奖项编号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>建议奖项名称</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>颁奖嘉宾 1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>颁奖嘉宾 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>年度 AI 商业化落地·领军企业奖</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>白硕（主旨 1）</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>缪川 / 笪浩（绿城中国）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>二</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>年度 AI 投资破局·领军机构奖</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>夏春 博士（主旨 2）</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>袁一栋（复金汇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>年度算力底座·战略生态奖</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>徐泳泽（腾讯云）</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>高歆（上海云基地，协办）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>四</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>年度新质资产创新奖</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>王维军（理事 / 主旨 3）</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>张露瑶 博士（昆山杜克）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>年度产业落地·标杆案例奖</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>李龙（龙旗科技 / 机器人）</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>于敬（达观数据）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>年度科技金融服务奖</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>林骁 / 陈煜（泰隆）</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>李睿（蔚来汽车）/ 华为鸿蒙汽车-代表</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>★ 5/22 09:00-11:00 物资统一入场 + 摆放顺序图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>区域编号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>物资</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>签收人</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>时间窗</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>一滴水正门 / 签到处</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>绿城品宣 KT 板（主入口背景）</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>葛九明</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>一滴水正门 / 签到处</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>蔚来汽车 易拉宝 + 礼品</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>葛九明</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>09:00-11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>一滴水正门 / 签到处</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>泰隆银行 易拉宝 + 客户伴手礼</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>葛九明</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>09:00-11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>一滴水正门 / 签到处</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>复金汇 易拉宝 + 签到礼品</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>马磊</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>09:00-11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>入口外</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>一滴水入口外（车位）</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>★ 华为鸿蒙汽车 展车（先到位）</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>葛九明、李正超</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>大厅展区</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>茶活力 中场茶歇区 + 体验台</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>蔡萍</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>09:00-11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>大厅展区</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>美年大健康 健康检测体验台</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>蔡萍</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>09:00-11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>大厅展区</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>蔚来汽车 易拉宝（不展车）</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>蔡萍</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>09:00-11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>主舞台 / 论坛厅</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>腾讯云 LOGO 墙 / 易拉宝（主舞台两侧）</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>葛九明</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>09:00-11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>主舞台 / 论坛厅</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>绿城品宣（大屏侧 / 签到墙）</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>葛九明</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>09:00-11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>主舞台 / 论坛厅</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>颁奖区台面（组委会准备 ★）</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>张蒙</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>11:00-12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>晚宴厅（二楼）</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>绿城【绿城·潮鸣】KT 板（晚宴入口）</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>张蒙</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>09:00-11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>晚宴厅（二楼）</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>绿城定制礼品 ×500（每席一份）</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>张蒙</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>09:00-11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>晚宴厅（二楼）</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>古井贡酒 20 瓶 + 礼盒（T01-T10 每桌 2 瓶）</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>张蒙</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>09:00-11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>晚宴厅（二楼）</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>泰隆物料（T05 虹口 / T06 杨浦 双桌）</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>葛九明</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>09:00-11:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2845,7 +4395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3848,7 +5398,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>绿城中国-嘉宾 1-5</t>
+          <t>缪川</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3858,12 +5408,12 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>冠名方代表</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>冠名方（预留 5 席）</t>
+          <t>晚宴冠名（每桌 1 人，共 42 位）</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -3880,22 +5430,22 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>周昭</t>
+          <t>笪浩</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>腾讯云</t>
+          <t>绿城中国</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>冠名方代表</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>战略合作伙伴</t>
+          <t>晚宴冠名（每桌 1 人，共 42 位）</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -3912,22 +5462,22 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>徐泳泽</t>
+          <t>绿城中国-嘉宾 3-5</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>腾讯云</t>
+          <t>绿城中国</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>华东区渠道总经理</t>
+          <t>待补</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>战略合作伙伴</t>
+          <t>冠名方</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -3944,7 +5494,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>孙总</t>
+          <t>周昭</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3976,7 +5526,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>李海洋</t>
+          <t>徐泳泽</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3986,7 +5536,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>华东区渠道总经理</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -4008,22 +5558,22 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>杨红江</t>
+          <t>孙总</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>泰隆银行上海分行</t>
+          <t>腾讯云</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>副行长</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>特约赞助商</t>
+          <t>战略合作伙伴</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -4040,22 +5590,22 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>汤梦薇</t>
+          <t>李海洋</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>泰隆银行上海分行</t>
+          <t>腾讯云</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>员工</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>特约赞助商</t>
+          <t>战略合作伙伴</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -4072,22 +5622,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>林骁</t>
+          <t>李睿</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>泰隆银行虹口支行</t>
+          <t>蔚来汽车</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>支行行长</t>
+          <t>对接人</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>特约赞助商</t>
+          <t>特约赞助商（不展车）</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -4104,22 +5654,22 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>陈煜</t>
+          <t>华为鸿蒙汽车-代表</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>泰隆银行杨浦支行</t>
+          <t>华为鸿蒙汽车</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>支行行长</t>
+          <t>待补</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>特约赞助商</t>
+          <t>特约赞助商（展车 ★）</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -4136,17 +5686,17 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>赵逸飞</t>
+          <t>林骁</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>泰隆银行杨浦支行</t>
+          <t>泰隆银行虹口支行</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>客户经理</t>
+          <t>支行行长</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -4168,7 +5718,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>晋嘉乐</t>
+          <t>陈煜</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -4178,7 +5728,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>客户经理</t>
+          <t>支行行长</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -4200,22 +5750,22 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>袁一栋</t>
+          <t>赵逸飞</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>复金汇</t>
+          <t>泰隆银行杨浦支行</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>合伙人 / 15995991077</t>
+          <t>客户经理</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>赞助方</t>
+          <t>特约赞助商</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -4225,191 +5775,191 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>八、行业 VIP / 一般出席嘉宾（绿色 ●）—— 节选</t>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>晋嘉乐</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>泰隆银行杨浦支行</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>客户经理</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>特约赞助商</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>橙 ●</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>李莺莺</t>
+          <t>孟高举</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>启力资本</t>
+          <t>茶活力</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>创始合伙人</t>
+          <t>对接人</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赞助方</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>绿 ●</t>
+          <t>橙 ●</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>王泓渊</t>
+          <t>鲁菲菲</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>欣日科技</t>
+          <t>美年大健康</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>财务经理</t>
+          <t>对接人</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赞助方</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>绿 ●</t>
+          <t>橙 ●</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>赵梓翔</t>
+          <t>袁一栋</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>兴业银行</t>
+          <t>复金汇</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>投资经理</t>
+          <t>合伙人 / 15995991077</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赞助方</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>绿 ●</t>
+          <t>橙 ●</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>魏军</t>
+          <t>李旭欢</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>中国投资协会新基建专委会</t>
+          <t>古井贡酒·年份原浆</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>副秘书长</t>
+          <t>对接人</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>赞助方</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>绿 ●</t>
+          <t>橙 ●</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>张稳</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>乐达产业</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>副总裁、合作发展部总经理</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>绿 ●</t>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>八、行业 VIP / 一般出席嘉宾（绿色 ●）—— 节选；杨红江 / 汤梦薇 已取消</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>邵彩霞</t>
+          <t>李莺莺</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>鲲腾能科 / 鲲腾资本</t>
+          <t>启力资本</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>创始合伙人</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -4426,22 +5976,22 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>苏燕春</t>
+          <t>王泓渊</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>上海汉蔚</t>
+          <t>欣日科技</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>总务</t>
+          <t>财务经理</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -4458,22 +6008,22 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>王金珂</t>
+          <t>赵梓翔</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>浙江一谦生态农业</t>
+          <t>兴业银行</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>总经理</t>
+          <t>投资经理</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -4490,22 +6040,22 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>唐亮</t>
+          <t>魏军</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>国网公司</t>
+          <t>中国投资协会新基建专委会</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>项目经理</t>
+          <t>副秘书长</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -4522,22 +6072,22 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>李克勤</t>
+          <t>张稳</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>瑞瓴股权投资管理</t>
+          <t>乐达产业</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>投资总监</t>
+          <t>副总裁、合作发展部总经理</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -4554,22 +6104,22 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>刘中原</t>
+          <t>邵彩霞</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>长江产业金融</t>
+          <t>鲲腾能科 / 鲲腾资本</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>产融发展部总经理</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -4586,22 +6136,22 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>张蒙</t>
+          <t>苏燕春</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>上海銮躅网络科技</t>
+          <t>上海汉蔚</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>董事长</t>
+          <t>总务</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -4618,22 +6168,22 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>谈英豪</t>
+          <t>王金珂</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>上海派米雷投资集团</t>
+          <t>浙江一谦生态农业</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>副总经理</t>
+          <t>总经理</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -4650,22 +6200,22 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>张戟</t>
+          <t>唐亮</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>上海方略咨询</t>
+          <t>国网公司</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>董事长</t>
+          <t>项目经理</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -4682,22 +6232,22 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>王梦</t>
+          <t>李克勤</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>上海煊物文化发展</t>
+          <t>瑞瓴股权投资管理</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>总经理</t>
+          <t>投资总监</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -4714,22 +6264,22 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>黄勇</t>
+          <t>刘中原</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>上海煊物文化发展</t>
+          <t>长江产业金融</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>董事长</t>
+          <t>产融发展部总经理</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -4746,22 +6296,22 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>陈颖芳</t>
+          <t>张蒙</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>邮储银行上海分行</t>
+          <t>上海銮躅网络科技</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>科技金融高级副经理</t>
+          <t>董事长</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -4778,22 +6328,22 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>冯浩然</t>
+          <t>谈英豪</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>上海茂专互联网金融</t>
+          <t>上海派米雷投资集团</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>副总经理</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -4810,22 +6360,22 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>罗晓</t>
+          <t>张戟</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>海南创意投资集团</t>
+          <t>上海方略咨询</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>执行董事</t>
+          <t>董事长</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -4842,22 +6392,22 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>潘健慧</t>
+          <t>王梦</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>安永会计师事务所</t>
+          <t>上海煊物文化发展</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>合伙人</t>
+          <t>总经理</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -4874,22 +6424,22 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>王梦雅</t>
+          <t>黄勇</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>吉梵资产</t>
+          <t>上海煊物文化发展</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>执行董事</t>
+          <t>董事长</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -4906,22 +6456,22 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>郭紫奇</t>
+          <t>陈颖芳</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>双安资产</t>
+          <t>邮储银行上海分行</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>高级研究员</t>
+          <t>科技金融高级副经理</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -4938,22 +6488,22 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>林雪</t>
+          <t>冯浩然</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>前景搜索资本</t>
+          <t>上海茂专互联网金融</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>管理合伙人</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -4970,22 +6520,22 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>张涌</t>
+          <t>罗晓</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>北京德和衡律师事务所</t>
+          <t>海南创意投资集团</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>合伙人</t>
+          <t>执行董事</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -5002,22 +6552,22 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>杨知予</t>
+          <t>潘健慧</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>隆基香港实业</t>
+          <t>安永会计师事务所</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>副总裁</t>
+          <t>合伙人</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -5034,22 +6584,22 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>任广焕</t>
+          <t>王梦雅</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>隆基香港实业</t>
+          <t>吉梵资产</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>董事长</t>
+          <t>执行董事</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -5066,22 +6616,22 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>周舟</t>
+          <t>郭紫奇</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>复旦大学管理学院</t>
+          <t>双安资产</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>副教授</t>
+          <t>高级研究员</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -5098,22 +6648,22 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>蔡建华</t>
+          <t>林雪</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>上海市普陀区机械工程学会</t>
+          <t>前景搜索资本</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>会长</t>
+          <t>管理合伙人</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -5130,22 +6680,22 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>杨峰</t>
+          <t>张涌</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>中天汇富教育产业集团</t>
+          <t>北京德和衡律师事务所</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>集团合伙人</t>
+          <t>合伙人</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -5162,22 +6712,22 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>田甜</t>
+          <t>杨知予</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>上海横排科技</t>
+          <t>隆基香港实业</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>副总裁</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -5194,22 +6744,22 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>唐伟</t>
+          <t>任广焕</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>上海晓棠科技</t>
+          <t>隆基香港实业</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>董事长</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -5226,22 +6776,22 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>邱诗灵</t>
+          <t>周舟</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>蔚力迪环境科技工程</t>
+          <t>复旦大学管理学院</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>副教授</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -5258,22 +6808,22 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>刘晓</t>
+          <t>蔡建华</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>上海市青浦新时代信息技术应用中心</t>
+          <t>上海市普陀区机械工程学会</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>副秘书长</t>
+          <t>会长</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -5290,22 +6840,22 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>姜逸斐</t>
+          <t>杨峰</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>上海逸斗科技</t>
+          <t>中天汇富教育产业集团</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>集团合伙人</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -5322,22 +6872,22 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>刘刚</t>
+          <t>田甜</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>上海盈通实业发展</t>
+          <t>上海横排科技</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>公司负责人</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -5354,22 +6904,22 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>腾健</t>
+          <t>唐伟</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>上海琪瓦丽科技</t>
+          <t>上海晓棠科技</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>公司负责人</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -5386,22 +6936,22 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>申垚</t>
+          <t>邱诗灵</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>上海博镁讯智能技术</t>
+          <t>蔚力迪环境科技工程</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>公司负责人</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -5418,22 +6968,22 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>丁懿</t>
+          <t>刘晓</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>上海乐西医疗器械</t>
+          <t>上海市青浦新时代信息技术应用中心</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>公司负责人</t>
+          <t>副秘书长</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -5450,22 +7000,22 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>孙珂</t>
+          <t>姜逸斐</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>上海秀群信息技术</t>
+          <t>上海逸斗科技</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>公司负责人</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -5482,22 +7032,22 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>李柳阳</t>
+          <t>刘刚</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>上海秀群信息技术</t>
+          <t>上海盈通实业发展</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>财务总监</t>
+          <t>公司负责人</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -5514,22 +7064,22 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>张钦</t>
+          <t>腾健</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>上海睿为通信技术</t>
+          <t>上海琪瓦丽科技</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>实控人 / 总经理</t>
+          <t>公司负责人</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -5546,22 +7096,22 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>李磊</t>
+          <t>申垚</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>上海宁坤信息科技</t>
+          <t>上海博镁讯智能技术</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>实控人 / 总经理</t>
+          <t>公司负责人</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -5578,22 +7128,22 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>高歆</t>
+          <t>丁懿</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>上海云基地</t>
+          <t>上海乐西医疗器械</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>副总经理</t>
+          <t>公司负责人</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -5610,22 +7160,22 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>顾炯亮</t>
+          <t>孙珂</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>上海云基地</t>
+          <t>上海秀群信息技术</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>顾问</t>
+          <t>公司负责人</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -5642,22 +7192,22 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>陈艳</t>
+          <t>李柳阳</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>碧云集团</t>
+          <t>上海秀群信息技术</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>总经理</t>
+          <t>财务总监</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -5674,22 +7224,22 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>孔华威</t>
+          <t>张钦</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>上海睿为通信技术</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>实控人 / 总经理</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -5706,27 +7256,27 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>葛九明</t>
+          <t>李磊</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>上海宁坤信息科技</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>实控人 / 总经理</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>（同志愿者 D 组）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -5738,22 +7288,22 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>朱震</t>
+          <t>高歆</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>上海云基地</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>副总经理</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -5770,22 +7320,22 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>王晓明</t>
+          <t>顾炯亮</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>上海云基地</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>顾问</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -5802,22 +7352,22 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>乐琪文</t>
+          <t>陈艳</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>碧云集团</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>总经理</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -5834,12 +7384,12 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>刘严</t>
+          <t>孔华威</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -5854,7 +7404,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>（志愿者 G 组）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -5866,30 +7416,190 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>葛九明</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>（同志愿者 D 组）</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>绿 ●</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>朱震</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>绿 ●</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>王晓明</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>绿 ●</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>乐琪文</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>绿 ●</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>刘严</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>（志愿者 G 组）</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>绿 ●</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>唐忠敏</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>绿 ●</t>
         </is>
@@ -5903,9 +7613,9 @@
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A55:F55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9006,7 +10716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9134,14 +10844,14 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>四、★ 颁奖典礼·高光启幕（14:25-14:40）</t>
+          <t>四、★ 颁奖典礼·高光启幕（14:25-14:40） — 黄欣不参加 / 福布斯不参与</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>主礼嘉宾 1</t>
+          <t>主礼致辞</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -9163,7 +10873,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>主礼嘉宾 2</t>
+          <t>颁奖主持</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -9185,190 +10895,205 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>主礼嘉宾 3</t>
+          <t>颁奖嘉宾 1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>黄欣</t>
+          <t>缪川 / 笪浩</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>国联安基金 / 北大经院上海校友会</t>
+          <t>绿城中国</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>秘书长</t>
+          <t>晚宴冠名战略合作伙伴</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>主礼嘉宾 4</t>
+          <t>颁奖嘉宾 2</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福布斯中国-代表</t>
+          <t>徐泳泽</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>福布斯中国 AI 评选委员会</t>
+          <t>腾讯云</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>华东区渠道总经理（战略合作伙伴）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>主礼嘉宾 5</t>
+          <t>颁奖嘉宾 3</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>绿城中国-代表</t>
+          <t>白硕</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>绿城中国</t>
+          <t>恒生电子研究院</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>院长（主旨 1 嘉宾）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>五、圆桌论坛一 · AI 硬核圆桌（14:40-15:20）</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>颁奖嘉宾 4</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>夏春 博士</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>香港国际金融学会</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>副会长（主旨 2 嘉宾）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>主持位</t>
+          <t>颁奖嘉宾 5</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>王维军</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>北京大学经济学院上海校友会</t>
+          <t>泓塬资产</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>理事</t>
+          <t>董事长（主旨 3 + 理事）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>嘉宾位 1</t>
+          <t>颁奖嘉宾 6</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>白硕</t>
+          <t>高歆</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>恒生电子研究院</t>
+          <t>上海市云计算创新基地</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>院长、首席科学家</t>
+          <t>副总经理（协办单位）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>嘉宾位 2</t>
+          <t>颁奖嘉宾 7</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>李龙</t>
+          <t>林骁 / 陈煜</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>龙旗科技</t>
+          <t>泰隆银行</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>机器人业务部总经理、思行 AI 联合创始人</t>
+          <t>支行行长（特约赞助商）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>嘉宾位 3</t>
+          <t>颁奖嘉宾 8</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>齐宝鑫</t>
+          <t>李睿 / 华为鸿蒙汽车-代表</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>上海市锦天城律师事务所</t>
+          <t>蔚来汽车 / 华为鸿蒙汽车</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>高级合伙人</t>
+          <t>特约赞助商</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>嘉宾位 4</t>
+          <t>颁奖嘉宾 9</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>刘文平</t>
+          <t>袁一栋</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>复金汇</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>能源专家、原上市公司董事长</t>
+          <t>合伙人（赞助方）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>六、圆桌论坛二 · 巅峰对话（15:20-16:00）</t>
+          <t>五、圆桌论坛一 · AI 硬核圆桌（14:40-15:20）</t>
         </is>
       </c>
     </row>
@@ -9380,17 +11105,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>胡继刚</t>
+          <t>王珏</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>复旦住房政策研究中心 / 杨浦科企联</t>
+          <t>北京大学经济学院上海校友会</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>秘书长 / 执行会长</t>
+          <t>理事</t>
         </is>
       </c>
     </row>
@@ -9402,17 +11127,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>刘帅华</t>
+          <t>白硕</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>火山引擎</t>
+          <t>恒生电子研究院</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>上海央国企业务负责人</t>
+          <t>院长、首席科学家</t>
         </is>
       </c>
     </row>
@@ -9424,17 +11149,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>徐泳泽</t>
+          <t>李龙</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>腾讯云</t>
+          <t>龙旗科技</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>产业生态合作部华东区渠道总经理</t>
+          <t>机器人业务部总经理、思行 AI 联合创始人</t>
         </is>
       </c>
     </row>
@@ -9446,17 +11171,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>黎远</t>
+          <t>齐宝鑫</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>福世合仑信息科技</t>
+          <t>上海市锦天城律师事务所</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>副总裁</t>
+          <t>高级合伙人</t>
         </is>
       </c>
     </row>
@@ -9468,241 +11193,358 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>刘剑英</t>
+          <t>刘文平</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>上海仪电智算科技</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>商务生态总监</t>
+          <t>能源专家、原上市公司董事长</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>嘉宾位 5</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>于敬</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>达观数据</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>联合创始人</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>六、圆桌论坛二 · 巅峰对话（15:20-16:00）</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>七、主旨演讲 3（16:50-17:10）</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>主持位</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>胡继刚</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>复旦住房政策研究中心 / 杨浦科企联</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>秘书长 / 执行会长</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>演讲台</t>
+          <t>嘉宾位 1</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>王维军</t>
+          <t>刘帅华</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>泓塬资产管理有限公司</t>
+          <t>火山引擎</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>董事长兼总经理</t>
+          <t>上海央国企业务负责人</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>八、主旨演讲 4（17:10-17:30）</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>嘉宾位 2</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>徐泳泽</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>腾讯云</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>产业生态合作部华东区渠道总经理（颁奖嘉宾）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>演讲台</t>
+          <t>嘉宾位 3</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>寇文红</t>
+          <t>黎远</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>《跨越自然利率陷阱》作者</t>
+          <t>福世合仑信息科技</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>副总裁</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>九、主旨演讲 5（17:30-17:50）</t>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>嘉宾位 4</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>刘剑英</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>上海仪电智算科技</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>商务生态总监</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>演讲台</t>
+          <t>嘉宾位 5</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>张露瑶 博士</t>
+          <t>于敬</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>昆山杜克大学 / 北大经院 2008 级</t>
+          <t>达观数据</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>助理教授</t>
+          <t>联合创始人</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>十、圆桌论坛三 · 投资大圆桌+闭幕仪式（17:50-18:30）</t>
+          <t>七、主旨演讲 3（16:50-17:10）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>主持位</t>
+          <t>演讲台</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>黄欣</t>
+          <t>王维军</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>国联安基金 / 北大经院上海校友会</t>
+          <t>泓塬资产管理有限公司</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>量化投资部董事 / 秘书长</t>
+          <t>董事长兼总经理</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>嘉宾位 1</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>曲承东</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>招商银行资金运营中心</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>总经理助理</t>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>八、主旨演讲 4（17:10-17:30）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>嘉宾位 2</t>
+          <t>演讲台</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>刘胜利</t>
+          <t>寇文红</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>长江证券</t>
+          <t>《跨越自然利率陷阱》作者</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>金融工程首席分析师</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>嘉宾位 3</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>饶雪莹</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>金浦投资 / 北大金融校友联合会</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>合伙人 / 副会长</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>九、主旨演讲 5（17:30-17:50）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
+          <t>演讲台</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>张露瑶 博士</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>昆山杜克大学 / 北大经院 2008 级</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>助理教授</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>十、圆桌论坛三 · 投资大圆桌+闭幕仪式（17:50-18:30）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>主持位</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>黄欣</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>国联安基金 / 北大经院上海校友会</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>量化投资部董事 / 秘书长</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>嘉宾位 1</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>曲承东</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>招商银行资金运营中心</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>总经理助理</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>嘉宾位 2</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>刘胜利</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>长江证券</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>金融工程首席分析师</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>嘉宾位 3</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>饶雪莹</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>金浦投资 / 北大金融校友联合会</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>合伙人 / 副会长</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
           <t>嘉宾位 4</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>马俊杰</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>小马创业村 / 铂泉投资</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>董事长</t>
         </is>
@@ -9713,14 +11555,14 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9940,7 +11782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9981,192 +11823,192 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>A 组 · 签到引导</t>
+          <t>组委会核心岗位</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>核心</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>韦佳玉</t>
+          <t>胡继刚（总联系人）</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>17301836967</t>
+          <t>13262607888</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>签到引导</t>
+          <t>杨浦科企联执行会长 / 巅峰对话主持</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>核心</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>李政春</t>
+          <t>王胜（VIP 接待）</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>（手机待补）</t>
+          <t>13083003003</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>签到引导</t>
+          <t>VIP 接待负责人</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>B 组 · 台卡 / 物料管理</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>核心</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>韦佳玉（现场总协调）</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>17301836967</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>现场总协调（原 A 组）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>核心</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>王胜</t>
+          <t>陈潇 Kelly（会务统筹）</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>13083003003</t>
+          <t>15021307893</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>台卡 / 物料</t>
+          <t>原'整体校对'，统筹全场</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>核心</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>朱铭喆</t>
+          <t>洪小燕（摄影摄像）</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>13052247845</t>
+          <t>15021488859</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>台卡 / 物料</t>
+          <t>摄影摄像</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>蔡杰</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>13817597850</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>H Workspace, Partner</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>A 组 · 签到引导</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>江梳桐</t>
+          <t>韦佳玉</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>（“江江”16621274301，请短信）</t>
+          <t>17301836967</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>台卡 / 物料</t>
+          <t>现场总协调</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>C 组 · VIP 接待</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>李振春</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>（手机待补）</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>签到引导</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>陈潇 Kelly</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>15021307893</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>VIP 接待</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>B 组 · 台卡 / 物料管理</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>王珏（C 组组长 / 理事）</t>
+          <t>王胜</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>13817642219</t>
+          <t>13083003003</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -10178,489 +12020,563 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>冯墨</t>
+          <t>朱铭喆</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>18516636112</t>
+          <t>13052247845</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>上海阳光卓众律师事务所 高级顾问</t>
+          <t>台卡 / 物料</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>黄露</t>
+          <t>蔡杰</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>13916894630</t>
+          <t>13817597850</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>VIP 接待</t>
+          <t>H Workspace, Partner</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>吕志翔</t>
+          <t>江梳桐</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>18221145186</t>
+          <t>（“江江”16621274301，请短信）</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>VIP 接待</t>
+          <t>台卡 / 物料</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>D 组 · 圆桌论坛对接 / 上下场</t>
+          <t>C 组 · VIP 接待</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>葛九明</t>
+          <t>陈潇 Kelly</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>（手机待补）</t>
+          <t>15021307893</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>圆桌对接</t>
+          <t>会务统筹</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>李正超</t>
+          <t>王珏（理事）</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>（手机待补）</t>
+          <t>13817642219</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>圆桌对接</t>
+          <t>VIP 接待</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>E 组 · 晚宴布置 / 席卡</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>冯墨</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>18516636112</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>上海阳光卓众律师事务所 高级顾问</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>张卓</t>
+          <t>黄露</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>15123215101</t>
+          <t>13916894630</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>晚宴布置</t>
+          <t>VIP 接待</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>高辰辰</t>
+          <t>吕志翔</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>（手机待补）</t>
+          <t>18221145186</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>晚宴布置</t>
+          <t>VIP 接待</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>随圣博</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>15656979326</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>上海徒圣博学教育 CEO</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>D 组 · 圆桌论坛对接 / 上下场 / 物资签收</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>安淑娟</t>
+          <t>葛九明</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>13661612711</t>
+          <t>（手机待补）</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>上海钦合律师事务所，整体校对</t>
+          <t>圆桌对接 / 物资签收</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>F 组 · 印刷 / 物料</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>李正超</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>（手机待补）</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>圆桌对接 / 物资签收</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>朱俊峰</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>13061624195</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>印刷</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>E 组 · 晚宴布置 / 席卡</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>彭常丽</t>
+          <t>张卓</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>（手机待补）</t>
+          <t>15123215101</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>印刷</t>
+          <t>晚宴布置</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>张蒙</t>
+          <t>高辰辰</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>13167038908</t>
+          <t>（手机待补）</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>上海銮躅网络科技董事长 / 席卡责任人</t>
+          <t>晚宴布置</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>G 组 · 现场调度 / 摄影摄像支援</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>随圣博</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>15656979326</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>上海徒圣博学教育 CEO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>刘严</t>
+          <t>安淑娟</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>13045669405</t>
+          <t>13661612711</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>现场调度</t>
+          <t>上海钦合律师事务所</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>李兵</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>18017922868</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>康诺斯科技 CEO</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>F 组 · 印刷 / 物料</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>蔡萍</t>
+          <t>朱俊峰</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>13916579716</t>
+          <t>13061624195</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>现场调度</t>
+          <t>印刷</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>马磊</t>
+          <t>彭常丽</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>13391021287</t>
+          <t>（手机待补）</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>衡芯（上海）智库平台 创始合伙人</t>
+          <t>印刷</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>外部协作</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>张蒙</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>13167038908</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>上海銮躅网络科技董事长 / 席卡责任人</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>外</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>胡继刚（巅峰对话主持 / 总联系人）</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>13262607888</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>杨浦科企联执行会长</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>G 组 · 现场调度 / 摄影摄像支援</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>外</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>皮尔德小C</t>
+          <t>刘严</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>15339617481</t>
+          <t>13045669405</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>外部支持</t>
+          <t>现场调度</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>外</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>洪小燕｜摄影摄像</t>
+          <t>李兵</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>15021488859</t>
+          <t>18017922868</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>摄影摄像</t>
+          <t>康诺斯科技 CEO</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>蔡萍</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>13916579716</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>现场调度</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>马磊</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>13391021287</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>衡芯（上海）智库平台 创始合伙人</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>外部协作（参照分工表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
           <t>外</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>皮尔德小C</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>15339617481</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>外部支持</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>外</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>江江</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>16621274301</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>请短信</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A26:D26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
